--- a/export-excel-engine/src/main/resources/template/report_template_v3.xlsx
+++ b/export-excel-engine/src/main/resources/template/report_template_v3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test\demo\demo\src\main\resources\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test\excel-export-engine\export-excel-engine\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A590645-C1ED-4CDE-BC90-BE37F8164735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BACCF3F-D4FA-4142-8728-BEBAC0D09F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,7 +106,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +123,25 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -177,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -185,14 +204,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,17 +565,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
@@ -570,14 +592,14 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1"/>
@@ -586,66 +608,66 @@
       <c r="J3" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6" t="s">
         <v>24</v>
       </c>
     </row>
